--- a/data/trans_camb/P7_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P7_R-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 2,57</t>
+          <t>-1,76; 2,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 2,01</t>
+          <t>-2,37; 2,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 4,92</t>
+          <t>-2,57; 4,9</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 2,46</t>
+          <t>-4,32; 2,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,2; -1,9</t>
+          <t>-7,01; -1,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 6,64</t>
+          <t>-3,98; 6,42</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 1,78</t>
+          <t>-2,27; 1,79</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,11; -0,65</t>
+          <t>-4,2; -0,63</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 3,64</t>
+          <t>-2,46; 3,56</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-50,74; 132,78</t>
+          <t>-46,24; 162,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-59,24; 105,1</t>
+          <t>-59,56; 125,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-73,65; 286,52</t>
+          <t>-76,49; 255,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-47,9; 52,4</t>
+          <t>-51,38; 48,14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-85,67; -32,23</t>
+          <t>-85,22; -32,37</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-54,05; 128,54</t>
+          <t>-53,56; 120,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-38,38; 48,71</t>
+          <t>-41,12; 48,47</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-71,05; -13,57</t>
+          <t>-71,09; -13,25</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-49,48; 90,26</t>
+          <t>-47,71; 88,74</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 4,16</t>
+          <t>-0,81; 4,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 2,07</t>
+          <t>-2,42; 2,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 6,24</t>
+          <t>-0,07; 6,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 1,05</t>
+          <t>-6,23; 1,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-8,6; -1,85</t>
+          <t>-8,24; -1,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-11,32; -4,82</t>
+          <t>-11,58; -4,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 1,84</t>
+          <t>-2,49; 1,96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,45; -0,31</t>
+          <t>-4,18; -0,28</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,88; -0,07</t>
+          <t>-5,06; -0,19</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-16,96; 118,86</t>
+          <t>-15,52; 121,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-44,87; 61,63</t>
+          <t>-44,9; 69,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-13,19; 176,64</t>
+          <t>-7,97; 182,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-45,38; 11,35</t>
+          <t>-43,53; 11,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-61,76; -17,44</t>
+          <t>-60,76; -17,21</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-82,46; -44,59</t>
+          <t>-82,23; -43,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-27,85; 27,74</t>
+          <t>-27,64; 29,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-49,08; -4,19</t>
+          <t>-47,15; -3,74</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-55,69; -1,99</t>
+          <t>-56,88; -2,16</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 2,91</t>
+          <t>-3,81; 2,63</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 0,42</t>
+          <t>-5,93; 0,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 2,12</t>
+          <t>-4,96; 1,74</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 3,23</t>
+          <t>-4,78; 3,21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,81; -3,47</t>
+          <t>-10,78; -3,46</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,0; -4,68</t>
+          <t>-12,25; -4,64</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 2,03</t>
+          <t>-3,2; 1,83</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,69; -2,71</t>
+          <t>-7,63; -2,78</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-7,83; -2,63</t>
+          <t>-7,81; -2,76</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-33,7; 37,08</t>
+          <t>-32,44; 33,5</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-51,83; 6,15</t>
+          <t>-51,4; 7,86</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-44,72; 29,08</t>
+          <t>-44,79; 22,25</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-25,17; 21,39</t>
+          <t>-24,09; 21,67</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-55,72; -22,31</t>
+          <t>-54,87; -21,73</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-61,3; -29,51</t>
+          <t>-63,46; -30,95</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-22,01; 16,58</t>
+          <t>-21,73; 15,33</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-50,44; -21,35</t>
+          <t>-50,13; -21,65</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-52,39; -21,16</t>
+          <t>-51,5; -21,57</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 6,37</t>
+          <t>-2,53; 6,49</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,55; 9,24</t>
+          <t>0,82; 9,71</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-9,75; 4,57</t>
+          <t>-9,64; 4,74</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-10,09; 0,93</t>
+          <t>-9,79; 0,95</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-12,71; -2,8</t>
+          <t>-13,5; -3,2</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-15,74; -6,18</t>
+          <t>-15,81; -5,91</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 2,16</t>
+          <t>-4,81; 2,43</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 2,08</t>
+          <t>-5,0; 1,76</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-12,51; -2,53</t>
+          <t>-12,4; -2,2</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-15,16; 60,08</t>
+          <t>-18,36; 61,2</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,82; 87,29</t>
+          <t>4,47; 97,0</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-65,14; 37,1</t>
+          <t>-64,33; 38,95</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-32,56; 3,74</t>
+          <t>-31,92; 3,49</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-41,74; -11,09</t>
+          <t>-43,99; -12,87</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-50,02; -25,19</t>
+          <t>-50,99; -24,55</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-20,97; 11,9</t>
+          <t>-21,51; 13,18</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-21,42; 11,63</t>
+          <t>-22,43; 9,52</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-58,62; -13,27</t>
+          <t>-59,56; -11,42</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-10,81; 2,17</t>
+          <t>-10,38; 1,7</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-10,39; 2,01</t>
+          <t>-9,8; 1,63</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,14; 4,49</t>
+          <t>-7,09; 4,05</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-10,02; 4,15</t>
+          <t>-8,9; 4,95</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-11,1; 2,06</t>
+          <t>-11,46; 1,49</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-13,79; -1,57</t>
+          <t>-13,58; -2,26</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-8,15; 1,25</t>
+          <t>-7,72; 1,39</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-9,58; -0,09</t>
+          <t>-8,97; -0,1</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-8,77; -0,59</t>
+          <t>-9,1; -0,83</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-34,2; 8,17</t>
+          <t>-32,86; 7,0</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-32,23; 8,35</t>
+          <t>-31,45; 6,12</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-21,25; 18,94</t>
+          <t>-21,89; 16,61</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-22,66; 11,21</t>
+          <t>-20,47; 13,71</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-26,05; 5,1</t>
+          <t>-27,15; 4,18</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-30,84; -4,49</t>
+          <t>-31,01; -6,28</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-21,86; 4,07</t>
+          <t>-20,89; 4,66</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-25,53; -0,3</t>
+          <t>-24,21; 0,14</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-23,57; -1,83</t>
+          <t>-24,23; -2,57</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-9,05; 6,64</t>
+          <t>-8,62; 7,11</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-15,14; 0,24</t>
+          <t>-15,27; -0,42</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-16,91; -3,61</t>
+          <t>-16,94; -3,86</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-17,9; -2,63</t>
+          <t>-17,87; -2,92</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-19,24; -4,08</t>
+          <t>-18,72; -4,62</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-49,09; -16,16</t>
+          <t>-48,24; -15,25</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-11,4; -0,14</t>
+          <t>-11,28; -0,55</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-15,33; -4,41</t>
+          <t>-15,47; -4,85</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-36,86; -12,58</t>
+          <t>-36,22; -12,86</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-21,44; 19,59</t>
+          <t>-20,79; 20,38</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-36,1; 0,73</t>
+          <t>-37,37; -1,31</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-40,44; -10,86</t>
+          <t>-39,39; -11,32</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-28,73; -4,66</t>
+          <t>-29,21; -5,63</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-31,29; -7,21</t>
+          <t>-30,45; -8,32</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-81,15; -27,79</t>
+          <t>-78,17; -26,89</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-22,25; -0,39</t>
+          <t>-21,65; -0,97</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-29,94; -9,69</t>
+          <t>-30,11; -10,55</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-71,91; -26,56</t>
+          <t>-71,97; -26,8</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-6,45; 11,45</t>
+          <t>-7,05; 12,52</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-18,17; -1,05</t>
+          <t>-18,03; -1,2</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-17,91; -3,05</t>
+          <t>-18,72; -2,25</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-9,96; 4,78</t>
+          <t>-9,6; 5,29</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-14,19; 1,49</t>
+          <t>-13,95; 0,99</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-15,24; -2,47</t>
+          <t>-15,1; -2,3</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-6,15; 5,41</t>
+          <t>-6,16; 5,46</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-13,5; -1,39</t>
+          <t>-13,45; -1,79</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-14,68; -4,38</t>
+          <t>-14,44; -4,73</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-10,83; 23,14</t>
+          <t>-11,98; 24,88</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-30,63; -2,1</t>
+          <t>-30,36; -2,49</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-29,78; -6,18</t>
+          <t>-31,52; -4,52</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-13,32; 7,37</t>
+          <t>-13,06; 7,86</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-19,43; 2,2</t>
+          <t>-18,78; 1,66</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-20,63; -4,12</t>
+          <t>-20,63; -3,5</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-9,26; 8,73</t>
+          <t>-9,22; 9,01</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-20,0; -2,28</t>
+          <t>-20,32; -3,03</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-21,84; -7,16</t>
+          <t>-21,61; -7,82</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 2,9</t>
+          <t>-0,74; 2,88</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 1,82</t>
+          <t>-1,8; 1,81</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 2,91</t>
+          <t>-3,03; 3,0</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 0,26</t>
+          <t>-4,18; 0,25</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-6,81; -2,63</t>
+          <t>-6,76; -2,58</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-10,94; -4,09</t>
+          <t>-10,7; -4,01</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 0,84</t>
+          <t>-1,84; 1,03</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-3,87; -1,03</t>
+          <t>-3,66; -0,87</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-5,39; -1,11</t>
+          <t>-5,86; -1,23</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 19,81</t>
+          <t>-4,53; 19,69</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-10,43; 12,22</t>
+          <t>-10,81; 12,42</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-16,45; 19,1</t>
+          <t>-18,01; 19,7</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-13,6; 1,07</t>
+          <t>-14,19; 1,13</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-23,1; -9,44</t>
+          <t>-22,65; -9,4</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-37,41; -14,8</t>
+          <t>-37,15; -14,92</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-8,28; 3,91</t>
+          <t>-8,01; 4,81</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-16,73; -4,85</t>
+          <t>-16,11; -4,22</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-23,76; -4,93</t>
+          <t>-25,64; -5,73</t>
         </is>
       </c>
     </row>
